--- a/sources/2E_Manha_2_Bimestre.xlsx
+++ b/sources/2E_Manha_2_Bimestre.xlsx
@@ -61,7 +61,7 @@
     <x:t>Conselho Segundo Bimestre</x:t>
   </x:si>
   <x:si>
-    <x:t>263</x:t>
+    <x:t>313</x:t>
   </x:si>
   <x:si>
     <x:t>0 (Soma de todas as eletivas)</x:t>
@@ -198,325 +198,328 @@
     <x:t>5</x:t>
   </x:si>
   <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>92%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANA ELIZA HOLUBOVSKI DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANA GABRIELLE DA SILVA AMORIM SOUZA FERREIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>84%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>88%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANA LAURA DA CRUZ SILVERIO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>76%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARIANE FERREIRA DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>77%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEATRIZ DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>96%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BENICIO CAETANO GOES DE LIMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>63%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>87%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRUNO KAYQUE FRANCISCO DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CARLOS EDUARDO VARGAS DE ASSIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>82%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELESTINO LUSSIKILA MAMBIMBI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>97%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDUARDA DOS SANTOS ALMEIDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEOVANNA EDUARDA GOMES DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAZIELLY VIVIAN VIANA DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HENNZO GABRIEL RODRIGUES BASLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Transferido</x:t>
+  </x:si>
+  <x:si>
     <x:t>-</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANA ELIZA HOLUBOVSKI DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>71%</x:t>
+    <x:t>100%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISABELLA ADRIANA PARDINI GOMES JARDIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISADORA REDUA RONDINONE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Remanejamento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JÚLIA SILVA SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAUAN DOS SANTOS SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYLLANE JULIA DE ANDRADE FERRAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEONARDO COSTA DO NASCIMENTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETICIA MARTINS DE ASSIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARCOS VINICIOS NEGRI PONTES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARIA EDUARDA BARROS PAULO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARIA LUIZA RIBEIRO SOARES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARIA SABRINA CORREIA DO NASCIMENTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MATEUS GOBBE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MATHEUS DA CRUZ SOUZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIRELLY HONORATO CLAUDINO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MURILO RODRIGUES DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MURILO SILVA PEREZ VIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Não Comparecimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATHANNY RAICA DO NASCIMENTO COSTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NICKOLAS KAUÃ SANTOS DA CRUZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PABLO ROCHA BATISTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAULO SERGIO DA CRUZ SOUZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEDRO HENRICK PEREIRA DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEDRO HENRIQUE SOUZA OLIVEIRA MILITÃO</x:t>
   </x:si>
   <x:si>
     <x:t>80%</x:t>
   </x:si>
   <x:si>
-    <x:t>ANA GABRIELLE DA SILVA AMORIM SOUZA FERREIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>84%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>89%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANA LAURA DA CRUZ SILVERIO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>75%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>78%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARIANE FERREIRA DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>76%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEATRIZ DE OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>87%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>98%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BENICIO CAETANO GOES DE LIMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>81%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRUNO KAYQUE FRANCISCO DE OLIVEIRA</x:t>
+    <x:t>PHILIPE HUMBERTO VIEIRA ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAFAEL VIEIRA ARBOLEYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>59%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAFAELA GOMES DE LISBOA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REBECA ISAQUE DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARA FERREIRA GONCALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARAH VITORIA ALVES MEDEIROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VICTOR GABRIEL DA SILVA DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENZO BRITO DA SILVA SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISABELA GOMES DE LISBOA</x:t>
   </x:si>
   <x:si>
     <x:t>90%</x:t>
   </x:si>
   <x:si>
-    <x:t>94%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CARLOS EDUARDO VARGAS DE ASSIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELESTINO LUSSIKILA MAMBIMBI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>97%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDUARDA DOS SANTOS ALMEIDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>93%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEOVANNA EDUARDA GOMES DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>79%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAZIELLY VIVIAN VIANA DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>96%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HENNZO GABRIEL RODRIGUES BASLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Transferido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISABELLA ADRIANA PARDINI GOMES JARDIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>73%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>77%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISADORA REDUA RONDINONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Remanejamento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>82%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JÚLIA SILVA SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAUAN DOS SANTOS SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYLLANE JULIA DE ANDRADE FERRAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>88%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LEONARDO COSTA DO NASCIMENTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>86%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETICIA MARTINS DE ASSIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARCOS VINICIOS NEGRI PONTES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIA EDUARDA BARROS PAULO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIA LUIZA RIBEIRO SOARES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIA SABRINA CORREIA DO NASCIMENTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MATEUS GOBBE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MATHEUS DA CRUZ SOUZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>92%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIRELLY HONORATO CLAUDINO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>53%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MURILO RODRIGUES DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>74%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MURILO SILVA PEREZ VIANA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Não Comparecimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATHANNY RAICA DO NASCIMENTO COSTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NICKOLAS KAUÃ SANTOS DA CRUZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PABLO ROCHA BATISTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>63%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>52%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAULO SERGIO DA CRUZ SOUZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEDRO HENRICK PEREIRA DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>59%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>41%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEDRO HENRIQUE SOUZA OLIVEIRA MILITÃO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILIPE HUMBERTO VIEIRA ALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAFAEL VIEIRA ARBOLEYA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>56%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>68%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAFAELA GOMES DE LISBOA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REBECA ISAQUE DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARA FERREIRA GONCALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARAH VITORIA ALVES MEDEIROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VICTOR GABRIEL DA SILVA DE OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>72%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENZO BRITO DA SILVA SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISABELA GOMES DE LISBOA</x:t>
-  </x:si>
-  <x:si>
     <x:t>SARA EMANUELLI SATURNINO BAZAN</x:t>
   </x:si>
   <x:si>
     <x:t>JOAO PEDRO BORGES DA SILVA</x:t>
   </x:si>
   <x:si>
-    <x:t>62%</x:t>
+    <x:t>65%</x:t>
   </x:si>
   <x:si>
     <x:t>DAVI DA SILVA ALMEIDA FRANCISCO</x:t>
@@ -546,7 +549,7 @@
     <x:t>Aulas Dadas: 41</x:t>
   </x:si>
   <x:si>
-    <x:t>Aulas Dadas: 0</x:t>
+    <x:t>Aulas Dadas: 50</x:t>
   </x:si>
   <x:si>
     <x:t>Aulas Dadas: 18</x:t>
@@ -1596,19 +1599,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AN13" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO13" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP13" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ13" s="12">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AR13" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS13" s="12" t="s">
         <x:v>53</x:v>
@@ -1620,7 +1623,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AV13" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AW13" s="12" t="s">
         <x:v>52</x:v>
@@ -1656,18 +1659,18 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="BH13" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BI13" s="12">
         <x:v>51</x:v>
       </x:c>
       <x:c r="BJ13" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:62">
       <x:c r="A14" s="11" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B14" s="12" t="s">
         <x:v>47</x:v>
@@ -1676,7 +1679,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E14" s="12" t="s">
         <x:v>55</x:v>
@@ -1700,10 +1703,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="N14" s="12" t="s">
         <x:v>50</x:v>
@@ -1739,7 +1742,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="Y14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Z14" s="12" t="s">
         <x:v>50</x:v>
@@ -1751,7 +1754,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AC14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AD14" s="12" t="s">
         <x:v>50</x:v>
@@ -1763,7 +1766,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AG14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH14" s="12" t="s">
         <x:v>50</x:v>
@@ -1772,10 +1775,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AJ14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AK14" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL14" s="12" t="s">
         <x:v>50</x:v>
@@ -1784,13 +1787,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AN14" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO14" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AP14" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ14" s="12">
         <x:v>2</x:v>
@@ -1808,10 +1811,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AV14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AW14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AX14" s="12" t="s">
         <x:v>50</x:v>
@@ -1823,7 +1826,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA14" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BB14" s="12" t="s">
         <x:v>50</x:v>
@@ -1832,7 +1835,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="BD14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BE14" s="12" t="s">
         <x:v>55</x:v>
@@ -1841,21 +1844,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG14" s="12">
-        <x:v>76</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="BH14" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="BI14" s="12">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="BJ14" s="12" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="BI14" s="12">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="BJ14" s="12" t="s">
-        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:62">
       <x:c r="A15" s="11" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B15" s="12" t="s">
         <x:v>47</x:v>
@@ -1963,7 +1966,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AK15" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL15" s="12" t="s">
         <x:v>50</x:v>
@@ -1972,19 +1975,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AN15" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO15" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP15" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AR15" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS15" s="12" t="s">
         <x:v>52</x:v>
@@ -2011,7 +2014,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="BA15" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB15" s="12" t="s">
         <x:v>50</x:v>
@@ -2029,21 +2032,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG15" s="12">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BH15" s="12" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="BI15" s="12">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="BJ15" s="12" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="BI15" s="12">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="BJ15" s="12" t="s">
-        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:62">
       <x:c r="A16" s="11" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
         <x:v>47</x:v>
@@ -2052,7 +2055,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D16" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E16" s="12" t="s">
         <x:v>53</x:v>
@@ -2064,10 +2067,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H16" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I16" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J16" s="12" t="s">
         <x:v>50</x:v>
@@ -2106,7 +2109,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="V16" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="W16" s="12">
         <x:v>4</x:v>
@@ -2139,7 +2142,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AG16" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH16" s="12" t="s">
         <x:v>50</x:v>
@@ -2151,7 +2154,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK16" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AL16" s="12" t="s">
         <x:v>50</x:v>
@@ -2160,13 +2163,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AN16" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO16" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AP16" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ16" s="12">
         <x:v>4</x:v>
@@ -2217,13 +2220,13 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG16" s="12">
-        <x:v>65</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BH16" s="12" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="BI16" s="12">
-        <x:v>124</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="BJ16" s="12" t="s">
         <x:v>70</x:v>
@@ -2240,7 +2243,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D17" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E17" s="12" t="s">
         <x:v>55</x:v>
@@ -2267,7 +2270,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="M17" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="N17" s="12" t="s">
         <x:v>50</x:v>
@@ -2303,7 +2306,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="Y17" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Z17" s="12" t="s">
         <x:v>50</x:v>
@@ -2339,7 +2342,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AK17" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL17" s="12" t="s">
         <x:v>50</x:v>
@@ -2348,13 +2351,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AN17" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO17" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AP17" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ17" s="12">
         <x:v>5</x:v>
@@ -2372,7 +2375,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AV17" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AW17" s="12" t="s">
         <x:v>53</x:v>
@@ -2399,19 +2402,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="BE17" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BF17" s="12" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG17" s="12">
-        <x:v>66</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="BH17" s="12" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="BI17" s="12">
-        <x:v>136</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="BJ17" s="12" t="s">
         <x:v>72</x:v>
@@ -2428,7 +2431,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D18" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E18" s="12" t="s">
         <x:v>49</x:v>
@@ -2458,7 +2461,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="N18" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O18" s="12">
         <x:v>6</x:v>
@@ -2536,13 +2539,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AN18" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO18" s="12" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AP18" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ18" s="12">
         <x:v>6</x:v>
@@ -2584,7 +2587,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="BD18" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE18" s="12" t="s">
         <x:v>52</x:v>
@@ -2593,13 +2596,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="BG18" s="12">
-        <x:v>34</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="BH18" s="12" t="s">
         <x:v>75</x:v>
       </x:c>
       <x:c r="BI18" s="12">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="BJ18" s="12" t="s">
         <x:v>76</x:v>
@@ -2616,13 +2619,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D19" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E19" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="F19" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G19" s="12">
         <x:v>7</x:v>
@@ -2631,7 +2634,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="I19" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J19" s="12" t="s">
         <x:v>78</x:v>
@@ -2643,10 +2646,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="M19" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="N19" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="O19" s="12">
         <x:v>7</x:v>
@@ -2658,19 +2661,19 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="R19" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="S19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="T19" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="U19" s="12" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="V19" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="W19" s="12">
         <x:v>7</x:v>
@@ -2703,10 +2706,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AG19" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AH19" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AI19" s="12">
         <x:v>7</x:v>
@@ -2715,22 +2718,22 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AK19" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="AL19" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="AM19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AN19" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO19" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AP19" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ19" s="12">
         <x:v>7</x:v>
@@ -2739,22 +2742,22 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AS19" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AT19" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="AU19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AV19" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW19" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AX19" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="AY19" s="12">
         <x:v>7</x:v>
@@ -2763,16 +2766,16 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BA19" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BB19" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="BC19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="BD19" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE19" s="12" t="s">
         <x:v>55</x:v>
@@ -2781,21 +2784,21 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BG19" s="12">
-        <x:v>102</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="BH19" s="12" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BI19" s="12">
-        <x:v>109</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BJ19" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:62">
       <x:c r="A20" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
         <x:v>47</x:v>
@@ -2852,7 +2855,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="T20" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="U20" s="12" t="s">
         <x:v>53</x:v>
@@ -2879,7 +2882,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AC20" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AD20" s="12" t="s">
         <x:v>50</x:v>
@@ -2900,7 +2903,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AJ20" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AK20" s="12" t="s">
         <x:v>53</x:v>
@@ -2912,13 +2915,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AN20" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO20" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP20" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ20" s="12">
         <x:v>8</x:v>
@@ -2969,21 +2972,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG20" s="12">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="BH20" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="BI20" s="12">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="BJ20" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:62">
       <x:c r="A21" s="11" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B21" s="12" t="s">
         <x:v>47</x:v>
@@ -2992,7 +2995,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D21" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E21" s="12" t="s">
         <x:v>55</x:v>
@@ -3100,13 +3103,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AN21" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO21" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AP21" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ21" s="12">
         <x:v>9</x:v>
@@ -3127,7 +3130,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AW21" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AX21" s="12" t="s">
         <x:v>50</x:v>
@@ -3136,10 +3139,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AZ21" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA21" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BB21" s="12" t="s">
         <x:v>50</x:v>
@@ -3151,27 +3154,27 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="BE21" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BF21" s="12" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG21" s="12">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BH21" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="BI21" s="12">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="BJ21" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:62">
       <x:c r="A22" s="11" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
         <x:v>47</x:v>
@@ -3180,7 +3183,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D22" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E22" s="12" t="s">
         <x:v>50</x:v>
@@ -3228,7 +3231,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="T22" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="U22" s="12" t="s">
         <x:v>50</x:v>
@@ -3276,7 +3279,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AJ22" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AK22" s="12" t="s">
         <x:v>50</x:v>
@@ -3288,19 +3291,19 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AN22" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO22" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP22" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AR22" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS22" s="12" t="s">
         <x:v>52</x:v>
@@ -3348,18 +3351,18 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="BH22" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI22" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="BJ22" s="12" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:62">
       <x:c r="A23" s="11" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
         <x:v>47</x:v>
@@ -3368,7 +3371,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D23" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E23" s="12" t="s">
         <x:v>49</x:v>
@@ -3476,19 +3479,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AN23" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO23" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP23" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="AR23" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS23" s="12" t="s">
         <x:v>52</x:v>
@@ -3512,7 +3515,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AZ23" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BA23" s="12" t="s">
         <x:v>52</x:v>
@@ -3524,7 +3527,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="BD23" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE23" s="12" t="s">
         <x:v>49</x:v>
@@ -3533,21 +3536,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG23" s="12">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="BH23" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="BI23" s="12">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="BJ23" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:62">
       <x:c r="A24" s="11" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
         <x:v>47</x:v>
@@ -3610,7 +3613,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="V24" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="W24" s="12">
         <x:v>12</x:v>
@@ -3664,13 +3667,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AN24" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO24" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AP24" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ24" s="12">
         <x:v>12</x:v>
@@ -3703,7 +3706,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA24" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB24" s="12" t="s">
         <x:v>50</x:v>
@@ -3715,27 +3718,27 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BE24" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BF24" s="12" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG24" s="12">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BH24" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="BI24" s="12">
-        <x:v>110</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="BJ24" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:62">
       <x:c r="A25" s="11" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
         <x:v>47</x:v>
@@ -3744,7 +3747,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D25" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E25" s="12" t="s">
         <x:v>50</x:v>
@@ -3768,7 +3771,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="L25" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M25" s="12" t="s">
         <x:v>53</x:v>
@@ -3804,7 +3807,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="X25" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y25" s="12" t="s">
         <x:v>52</x:v>
@@ -3852,19 +3855,19 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AN25" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO25" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP25" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ25" s="12">
         <x:v>13</x:v>
       </x:c>
       <x:c r="AR25" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS25" s="12" t="s">
         <x:v>50</x:v>
@@ -3900,7 +3903,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="BD25" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE25" s="12" t="s">
         <x:v>50</x:v>
@@ -3909,16 +3912,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG25" s="12">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="BH25" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI25" s="12">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="BJ25" s="12" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:62">
@@ -3932,7 +3935,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E26" s="12" t="s">
         <x:v>50</x:v>
@@ -3944,7 +3947,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="H26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="I26" s="12" t="s">
         <x:v>50</x:v>
@@ -3956,7 +3959,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="L26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="M26" s="12" t="s">
         <x:v>50</x:v>
@@ -3968,7 +3971,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="P26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Q26" s="12" t="s">
         <x:v>50</x:v>
@@ -3980,7 +3983,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="T26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="U26" s="12" t="s">
         <x:v>50</x:v>
@@ -3992,7 +3995,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="X26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Y26" s="12" t="s">
         <x:v>50</x:v>
@@ -4004,7 +4007,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AB26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AC26" s="12" t="s">
         <x:v>50</x:v>
@@ -4016,7 +4019,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AF26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AG26" s="12" t="s">
         <x:v>50</x:v>
@@ -4028,7 +4031,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AJ26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AK26" s="12" t="s">
         <x:v>50</x:v>
@@ -4040,19 +4043,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AN26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AO26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="AR26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AS26" s="12" t="s">
         <x:v>50</x:v>
@@ -4064,7 +4067,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AV26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AW26" s="12" t="s">
         <x:v>50</x:v>
@@ -4076,7 +4079,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AZ26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BA26" s="12" t="s">
         <x:v>50</x:v>
@@ -4088,30 +4091,30 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="BD26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BE26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BF26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BG26" s="12">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BH26" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="BI26" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="BJ26" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:62">
       <x:c r="A27" s="11" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B27" s="12" t="s">
         <x:v>47</x:v>
@@ -4168,7 +4171,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="T27" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="U27" s="12" t="s">
         <x:v>50</x:v>
@@ -4180,7 +4183,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="X27" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y27" s="12" t="s">
         <x:v>53</x:v>
@@ -4195,7 +4198,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AC27" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AD27" s="12" t="s">
         <x:v>50</x:v>
@@ -4216,10 +4219,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AJ27" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AK27" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL27" s="12" t="s">
         <x:v>50</x:v>
@@ -4228,13 +4231,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AN27" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO27" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AP27" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ27" s="12">
         <x:v>15</x:v>
@@ -4243,10 +4246,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AS27" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AT27" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AU27" s="12">
         <x:v>15</x:v>
@@ -4255,7 +4258,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AW27" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX27" s="12" t="s">
         <x:v>50</x:v>
@@ -4285,16 +4288,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG27" s="12">
-        <x:v>71</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="BH27" s="12" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BI27" s="12">
-        <x:v>131</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="BJ27" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:62">
@@ -4308,7 +4311,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D28" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E28" s="12" t="s">
         <x:v>54</x:v>
@@ -4320,7 +4323,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H28" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="I28" s="12" t="s">
         <x:v>52</x:v>
@@ -4332,7 +4335,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="L28" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="M28" s="12" t="s">
         <x:v>53</x:v>
@@ -4344,7 +4347,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="P28" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Q28" s="12" t="s">
         <x:v>54</x:v>
@@ -4356,7 +4359,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="T28" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="U28" s="12" t="s">
         <x:v>52</x:v>
@@ -4368,7 +4371,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="X28" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Y28" s="12" t="s">
         <x:v>53</x:v>
@@ -4380,7 +4383,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AB28" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AC28" s="12" t="s">
         <x:v>55</x:v>
@@ -4392,7 +4395,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AF28" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AG28" s="12" t="s">
         <x:v>53</x:v>
@@ -4404,7 +4407,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AJ28" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AK28" s="12" t="s">
         <x:v>48</x:v>
@@ -4416,19 +4419,19 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AN28" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AO28" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP28" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="AR28" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AS28" s="12" t="s">
         <x:v>53</x:v>
@@ -4440,7 +4443,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AV28" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AW28" s="12" t="s">
         <x:v>53</x:v>
@@ -4452,10 +4455,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AZ28" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BA28" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB28" s="12" t="s">
         <x:v>50</x:v>
@@ -4464,25 +4467,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="BD28" s="12" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="BE28" s="12" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="BF28" s="12" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="BG28" s="12">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="BE28" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="BF28" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="BG28" s="12">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="BH28" s="12" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="BI28" s="12">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="BJ28" s="12" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="BI28" s="12">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="BJ28" s="12" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:62">
@@ -4496,7 +4499,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E29" s="12" t="s">
         <x:v>49</x:v>
@@ -4508,7 +4511,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="H29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="I29" s="12" t="s">
         <x:v>53</x:v>
@@ -4520,7 +4523,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="L29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="M29" s="12" t="s">
         <x:v>52</x:v>
@@ -4532,7 +4535,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Q29" s="12" t="s">
         <x:v>49</x:v>
@@ -4544,7 +4547,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="T29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="U29" s="12" t="s">
         <x:v>50</x:v>
@@ -4556,7 +4559,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="X29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Y29" s="12" t="s">
         <x:v>50</x:v>
@@ -4568,7 +4571,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AB29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AC29" s="12" t="s">
         <x:v>49</x:v>
@@ -4580,7 +4583,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AF29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AG29" s="12" t="s">
         <x:v>52</x:v>
@@ -4592,10 +4595,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AJ29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AK29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AL29" s="12" t="s">
         <x:v>50</x:v>
@@ -4604,19 +4607,19 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AN29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AO29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AP29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AR29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AS29" s="12" t="s">
         <x:v>52</x:v>
@@ -4628,7 +4631,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AV29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AW29" s="12" t="s">
         <x:v>52</x:v>
@@ -4640,7 +4643,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AZ29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BA29" s="12" t="s">
         <x:v>52</x:v>
@@ -4652,25 +4655,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="BD29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BE29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BF29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BG29" s="12">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="BH29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="BI29" s="12">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BJ29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:62">
@@ -4792,19 +4795,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AN30" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO30" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP30" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="AR30" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS30" s="12" t="s">
         <x:v>52</x:v>
@@ -4849,21 +4852,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG30" s="12">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="BH30" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BI30" s="12">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BJ30" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:62">
       <x:c r="A31" s="11" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B31" s="12" t="s">
         <x:v>47</x:v>
@@ -4872,7 +4875,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D31" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E31" s="12" t="s">
         <x:v>52</x:v>
@@ -4884,7 +4887,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H31" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I31" s="12" t="s">
         <x:v>52</x:v>
@@ -4908,7 +4911,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="P31" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q31" s="12" t="s">
         <x:v>52</x:v>
@@ -4932,7 +4935,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="X31" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y31" s="12" t="s">
         <x:v>50</x:v>
@@ -4956,7 +4959,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AF31" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG31" s="12" t="s">
         <x:v>52</x:v>
@@ -4968,7 +4971,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AJ31" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK31" s="12" t="s">
         <x:v>48</x:v>
@@ -4980,19 +4983,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AN31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AO31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="AR31" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS31" s="12" t="s">
         <x:v>53</x:v>
@@ -5016,7 +5019,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AZ31" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BA31" s="12" t="s">
         <x:v>53</x:v>
@@ -5028,7 +5031,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="BD31" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE31" s="12" t="s">
         <x:v>54</x:v>
@@ -5037,21 +5040,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG31" s="12">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="BH31" s="12" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="BI31" s="12">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BJ31" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:62">
       <x:c r="A32" s="11" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
         <x:v>47</x:v>
@@ -5147,7 +5150,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AG32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH32" s="12" t="s">
         <x:v>50</x:v>
@@ -5159,7 +5162,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK32" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL32" s="12" t="s">
         <x:v>50</x:v>
@@ -5168,13 +5171,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AN32" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO32" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP32" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ32" s="12">
         <x:v>20</x:v>
@@ -5183,7 +5186,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AS32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT32" s="12" t="s">
         <x:v>50</x:v>
@@ -5192,7 +5195,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AV32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW32" s="12" t="s">
         <x:v>51</x:v>
@@ -5225,16 +5228,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG32" s="12">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BH32" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="BI32" s="12">
-        <x:v>82</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="BJ32" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:62">
@@ -5260,7 +5263,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I33" s="12" t="s">
         <x:v>51</x:v>
@@ -5272,7 +5275,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="L33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M33" s="12" t="s">
         <x:v>52</x:v>
@@ -5296,7 +5299,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="T33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="U33" s="12" t="s">
         <x:v>50</x:v>
@@ -5308,7 +5311,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="X33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y33" s="12" t="s">
         <x:v>52</x:v>
@@ -5356,13 +5359,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AN33" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO33" s="12" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AP33" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ33" s="12">
         <x:v>21</x:v>
@@ -5395,7 +5398,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="BA33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB33" s="12" t="s">
         <x:v>50</x:v>
@@ -5413,21 +5416,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG33" s="12">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BH33" s="12" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="BI33" s="12">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="BJ33" s="12" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="BI33" s="12">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="BJ33" s="12" t="s">
-        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:62">
       <x:c r="A34" s="11" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
         <x:v>47</x:v>
@@ -5451,7 +5454,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I34" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J34" s="12" t="s">
         <x:v>50</x:v>
@@ -5463,16 +5466,16 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M34" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="N34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="P34" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q34" s="12" t="s">
         <x:v>50</x:v>
@@ -5499,7 +5502,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="Y34" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z34" s="12" t="s">
         <x:v>50</x:v>
@@ -5511,7 +5514,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AC34" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD34" s="12" t="s">
         <x:v>50</x:v>
@@ -5535,7 +5538,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK34" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL34" s="12" t="s">
         <x:v>50</x:v>
@@ -5544,13 +5547,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AN34" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO34" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP34" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ34" s="12">
         <x:v>22</x:v>
@@ -5580,7 +5583,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AZ34" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA34" s="12" t="s">
         <x:v>50</x:v>
@@ -5601,21 +5604,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG34" s="12">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BH34" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BI34" s="12">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="BJ34" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:62">
       <x:c r="A35" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B35" s="12" t="s">
         <x:v>47</x:v>
@@ -5624,7 +5627,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="D35" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E35" s="12" t="s">
         <x:v>49</x:v>
@@ -5660,7 +5663,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="P35" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q35" s="12" t="s">
         <x:v>49</x:v>
@@ -5684,7 +5687,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="X35" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y35" s="12" t="s">
         <x:v>50</x:v>
@@ -5720,7 +5723,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AJ35" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AK35" s="12" t="s">
         <x:v>49</x:v>
@@ -5732,13 +5735,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AN35" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO35" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP35" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ35" s="12">
         <x:v>23</x:v>
@@ -5792,13 +5795,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="BH35" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="BI35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="BJ35" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:62">
@@ -5812,7 +5815,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
         <x:v>54</x:v>
@@ -5824,7 +5827,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H36" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I36" s="12" t="s">
         <x:v>53</x:v>
@@ -5875,7 +5878,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="Y36" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Z36" s="12" t="s">
         <x:v>50</x:v>
@@ -5899,7 +5902,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AG36" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH36" s="12" t="s">
         <x:v>50</x:v>
@@ -5920,13 +5923,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AN36" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO36" s="12" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AP36" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ36" s="12">
         <x:v>24</x:v>
@@ -5959,7 +5962,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="BA36" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB36" s="12" t="s">
         <x:v>50</x:v>
@@ -5977,16 +5980,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG36" s="12">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="BH36" s="12" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="BI36" s="12">
-        <x:v>102</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BJ36" s="12" t="s">
-        <x:v>109</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:62">
@@ -6012,7 +6015,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="H37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I37" s="12" t="s">
         <x:v>50</x:v>
@@ -6027,7 +6030,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="M37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="N37" s="12" t="s">
         <x:v>50</x:v>
@@ -6036,7 +6039,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="P37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q37" s="12" t="s">
         <x:v>52</x:v>
@@ -6060,7 +6063,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="X37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y37" s="12" t="s">
         <x:v>53</x:v>
@@ -6075,7 +6078,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AC37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AD37" s="12" t="s">
         <x:v>50</x:v>
@@ -6096,7 +6099,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AJ37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AK37" s="12" t="s">
         <x:v>52</x:v>
@@ -6108,13 +6111,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AN37" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO37" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP37" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ37" s="12">
         <x:v>25</x:v>
@@ -6144,7 +6147,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AZ37" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BA37" s="12" t="s">
         <x:v>53</x:v>
@@ -6156,7 +6159,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="BD37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BE37" s="12" t="s">
         <x:v>52</x:v>
@@ -6165,16 +6168,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG37" s="12">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="BH37" s="12" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="BI37" s="12">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="BI37" s="12">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="BJ37" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:62">
@@ -6212,7 +6215,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="L38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M38" s="12" t="s">
         <x:v>52</x:v>
@@ -6287,7 +6290,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK38" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL38" s="12" t="s">
         <x:v>50</x:v>
@@ -6296,13 +6299,13 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AN38" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO38" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AP38" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ38" s="12">
         <x:v>26</x:v>
@@ -6335,7 +6338,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA38" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB38" s="12" t="s">
         <x:v>50</x:v>
@@ -6353,16 +6356,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG38" s="12">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BH38" s="12" t="s">
-        <x:v>117</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BI38" s="12">
-        <x:v>137</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="BJ38" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:62">
@@ -6388,7 +6391,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="H39" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I39" s="12" t="s">
         <x:v>52</x:v>
@@ -6484,19 +6487,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AN39" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO39" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP39" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="AR39" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AS39" s="12" t="s">
         <x:v>52</x:v>
@@ -6541,21 +6544,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG39" s="12">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="BH39" s="12" t="s">
-        <x:v>125</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BI39" s="12">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BJ39" s="12" t="s">
-        <x:v>125</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:62">
       <x:c r="A40" s="11" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B40" s="12" t="s">
         <x:v>47</x:v>
@@ -6567,7 +6570,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F40" s="12" t="s">
         <x:v>50</x:v>
@@ -6582,7 +6585,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="J40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K40" s="12">
         <x:v>28</x:v>
@@ -6591,7 +6594,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="M40" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="N40" s="12" t="s">
         <x:v>50</x:v>
@@ -6627,7 +6630,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="Y40" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z40" s="12" t="s">
         <x:v>50</x:v>
@@ -6639,7 +6642,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AC40" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AD40" s="12" t="s">
         <x:v>50</x:v>
@@ -6651,7 +6654,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AG40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH40" s="12" t="s">
         <x:v>50</x:v>
@@ -6663,7 +6666,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK40" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="AL40" s="12" t="s">
         <x:v>50</x:v>
@@ -6672,13 +6675,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AN40" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO40" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="AP40" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ40" s="12">
         <x:v>28</x:v>
@@ -6699,7 +6702,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AW40" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX40" s="12" t="s">
         <x:v>50</x:v>
@@ -6711,7 +6714,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA40" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="BB40" s="12" t="s">
         <x:v>50</x:v>
@@ -6723,27 +6726,27 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="BE40" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BF40" s="12" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG40" s="12">
-        <x:v>124</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="BH40" s="12" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="BI40" s="12">
-        <x:v>226</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="BJ40" s="12" t="s">
-        <x:v>86</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:62">
       <x:c r="A41" s="11" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B41" s="12" t="s">
         <x:v>47</x:v>
@@ -6764,7 +6767,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I41" s="12" t="s">
         <x:v>53</x:v>
@@ -6779,7 +6782,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="M41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="N41" s="12" t="s">
         <x:v>50</x:v>
@@ -6788,7 +6791,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="P41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q41" s="12" t="s">
         <x:v>54</x:v>
@@ -6803,10 +6806,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="U41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="V41" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="W41" s="12">
         <x:v>29</x:v>
@@ -6827,7 +6830,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AC41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AD41" s="12" t="s">
         <x:v>50</x:v>
@@ -6839,7 +6842,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AG41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH41" s="12" t="s">
         <x:v>50</x:v>
@@ -6848,10 +6851,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AJ41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AK41" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL41" s="12" t="s">
         <x:v>50</x:v>
@@ -6860,13 +6863,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AN41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AP41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ41" s="12">
         <x:v>29</x:v>
@@ -6875,7 +6878,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AS41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT41" s="12" t="s">
         <x:v>50</x:v>
@@ -6887,7 +6890,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AW41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AX41" s="12" t="s">
         <x:v>50</x:v>
@@ -6899,7 +6902,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB41" s="12" t="s">
         <x:v>50</x:v>
@@ -6917,30 +6920,30 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG41" s="12">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="BH41" s="12" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="BH41" s="12" t="s">
-        <x:v>130</x:v>
-      </x:c>
       <x:c r="BI41" s="12">
-        <x:v>103</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="BJ41" s="12" t="s">
-        <x:v>109</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:62">
       <x:c r="A42" s="11" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B42" s="12" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="B42" s="12" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="C42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E42" s="12" t="s">
         <x:v>54</x:v>
@@ -6952,10 +6955,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="I42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J42" s="12" t="s">
         <x:v>50</x:v>
@@ -6964,10 +6967,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="M42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="N42" s="12" t="s">
         <x:v>50</x:v>
@@ -6976,7 +6979,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="P42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Q42" s="12" t="s">
         <x:v>54</x:v>
@@ -6988,10 +6991,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="T42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="U42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="V42" s="12" t="s">
         <x:v>50</x:v>
@@ -7000,10 +7003,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="X42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Y42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Z42" s="12" t="s">
         <x:v>50</x:v>
@@ -7012,10 +7015,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AB42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AC42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AD42" s="12" t="s">
         <x:v>50</x:v>
@@ -7024,7 +7027,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AF42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AG42" s="12" t="s">
         <x:v>51</x:v>
@@ -7036,10 +7039,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AJ42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AK42" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AL42" s="12" t="s">
         <x:v>50</x:v>
@@ -7048,19 +7051,19 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AN42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AO42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AP42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="AR42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AS42" s="12" t="s">
         <x:v>51</x:v>
@@ -7072,7 +7075,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AV42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AW42" s="12" t="s">
         <x:v>51</x:v>
@@ -7084,10 +7087,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AZ42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BA42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB42" s="12" t="s">
         <x:v>50</x:v>
@@ -7096,25 +7099,25 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="BD42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BE42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BF42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BG42" s="12">
-        <x:v>80</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="BH42" s="12" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="BI42" s="12">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="BJ42" s="12" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="BI42" s="12">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="BJ42" s="12" t="s">
-        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:62">
@@ -7128,7 +7131,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="D43" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E43" s="12" t="s">
         <x:v>50</x:v>
@@ -7140,7 +7143,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H43" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I43" s="12" t="s">
         <x:v>53</x:v>
@@ -7152,7 +7155,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="L43" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M43" s="12" t="s">
         <x:v>53</x:v>
@@ -7224,10 +7227,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AJ43" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AK43" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AL43" s="12" t="s">
         <x:v>50</x:v>
@@ -7236,19 +7239,19 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AN43" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO43" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP43" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AR43" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AS43" s="12" t="s">
         <x:v>52</x:v>
@@ -7272,7 +7275,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AZ43" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA43" s="12" t="s">
         <x:v>50</x:v>
@@ -7293,16 +7296,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG43" s="12">
-        <x:v>36</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="BH43" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="BI43" s="12">
-        <x:v>41</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BJ43" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:62">
@@ -7316,7 +7319,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E44" s="12" t="s">
         <x:v>50</x:v>
@@ -7328,7 +7331,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I44" s="12" t="s">
         <x:v>50</x:v>
@@ -7424,13 +7427,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AN44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ44" s="12">
         <x:v>32</x:v>
@@ -7472,7 +7475,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="BD44" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE44" s="12" t="s">
         <x:v>49</x:v>
@@ -7481,13 +7484,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG44" s="12">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="BH44" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="BI44" s="12">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="BJ44" s="12" t="s">
         <x:v>136</x:v>
@@ -7498,13 +7501,13 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="B45" s="12" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="D45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E45" s="12" t="s">
         <x:v>54</x:v>
@@ -7516,10 +7519,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H45" s="12" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="I45" s="12" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="I45" s="12" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="J45" s="12" t="s">
         <x:v>50</x:v>
@@ -7528,7 +7531,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="L45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="M45" s="12" t="s">
         <x:v>51</x:v>
@@ -7540,7 +7543,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="P45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Q45" s="12" t="s">
         <x:v>53</x:v>
@@ -7552,7 +7555,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="T45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="U45" s="12" t="s">
         <x:v>51</x:v>
@@ -7564,7 +7567,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="X45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Y45" s="12" t="s">
         <x:v>51</x:v>
@@ -7576,7 +7579,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AB45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AC45" s="12" t="s">
         <x:v>48</x:v>
@@ -7588,10 +7591,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AF45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AG45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH45" s="12" t="s">
         <x:v>50</x:v>
@@ -7600,10 +7603,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AJ45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AK45" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="AL45" s="12" t="s">
         <x:v>50</x:v>
@@ -7612,19 +7615,19 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AN45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AO45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="AP45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AR45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AS45" s="12" t="s">
         <x:v>51</x:v>
@@ -7636,7 +7639,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AV45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AW45" s="12" t="s">
         <x:v>51</x:v>
@@ -7648,7 +7651,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AZ45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BA45" s="12" t="s">
         <x:v>51</x:v>
@@ -7660,22 +7663,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="BD45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BE45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BF45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BG45" s="12">
-        <x:v>97</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="BH45" s="12" t="s">
-        <x:v>138</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BI45" s="12">
-        <x:v>267</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="BJ45" s="12" t="s">
         <x:v>139</x:v>
@@ -7800,13 +7803,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AN46" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO46" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP46" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ46" s="12">
         <x:v>34</x:v>
@@ -7836,7 +7839,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AZ46" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA46" s="12" t="s">
         <x:v>52</x:v>
@@ -7857,16 +7860,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG46" s="12">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="BH46" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI46" s="12">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BJ46" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:62">
@@ -7880,7 +7883,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E47" s="12" t="s">
         <x:v>53</x:v>
@@ -7892,7 +7895,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="H47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="I47" s="12" t="s">
         <x:v>51</x:v>
@@ -7904,10 +7907,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L47" s="12" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="M47" s="12" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="M47" s="12" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="N47" s="12" t="s">
         <x:v>50</x:v>
@@ -7916,7 +7919,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="P47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Q47" s="12" t="s">
         <x:v>54</x:v>
@@ -7928,7 +7931,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="T47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="U47" s="12" t="s">
         <x:v>51</x:v>
@@ -7940,10 +7943,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="X47" s="12" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="Y47" s="12" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="Y47" s="12" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="Z47" s="12" t="s">
         <x:v>50</x:v>
@@ -7952,10 +7955,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AB47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AC47" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD47" s="12" t="s">
         <x:v>50</x:v>
@@ -7964,10 +7967,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AF47" s="12" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="AG47" s="12" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="AG47" s="12" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="AH47" s="12" t="s">
         <x:v>50</x:v>
@@ -7976,7 +7979,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AJ47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AK47" s="12" t="s">
         <x:v>142</x:v>
@@ -7988,22 +7991,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AN47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AO47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="AP47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="AR47" s="12" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="AS47" s="12" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="AS47" s="12" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="AT47" s="12" t="s">
         <x:v>50</x:v>
@@ -8012,10 +8015,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AV47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AW47" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AX47" s="12" t="s">
         <x:v>50</x:v>
@@ -8024,10 +8027,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AZ47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BA47" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB47" s="12" t="s">
         <x:v>50</x:v>
@@ -8036,22 +8039,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="BD47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BE47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BF47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BG47" s="12">
-        <x:v>107</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="BH47" s="12" t="s">
         <x:v>143</x:v>
       </x:c>
       <x:c r="BI47" s="12">
-        <x:v>329</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="BJ47" s="12" t="s">
         <x:v>144</x:v>
@@ -8083,7 +8086,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J48" s="12" t="s">
         <x:v>50</x:v>
@@ -8095,7 +8098,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="N48" s="12" t="s">
         <x:v>50</x:v>
@@ -8131,7 +8134,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="Y48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Z48" s="12" t="s">
         <x:v>50</x:v>
@@ -8155,7 +8158,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AG48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH48" s="12" t="s">
         <x:v>50</x:v>
@@ -8167,7 +8170,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK48" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AL48" s="12" t="s">
         <x:v>50</x:v>
@@ -8176,13 +8179,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AN48" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO48" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP48" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ48" s="12">
         <x:v>36</x:v>
@@ -8215,7 +8218,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="BA48" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BB48" s="12" t="s">
         <x:v>50</x:v>
@@ -8233,21 +8236,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG48" s="12">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="BH48" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BI48" s="12">
-        <x:v>120</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="BJ48" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:62">
       <x:c r="A49" s="11" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B49" s="12" t="s">
         <x:v>47</x:v>
@@ -8271,7 +8274,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="I49" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J49" s="12" t="s">
         <x:v>50</x:v>
@@ -8286,7 +8289,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="N49" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O49" s="12">
         <x:v>37</x:v>
@@ -8355,22 +8358,22 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK49" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL49" s="12" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="AM49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="AN49" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO49" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AP49" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ49" s="12">
         <x:v>37</x:v>
@@ -8394,7 +8397,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AX49" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AY49" s="12">
         <x:v>37</x:v>
@@ -8421,21 +8424,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG49" s="12">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="BH49" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="BI49" s="12">
-        <x:v>30</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="BJ49" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:62">
       <x:c r="A50" s="11" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B50" s="12" t="s">
         <x:v>47</x:v>
@@ -8459,7 +8462,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="I50" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J50" s="12" t="s">
         <x:v>50</x:v>
@@ -8468,10 +8471,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="L50" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M50" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="N50" s="12" t="s">
         <x:v>50</x:v>
@@ -8519,7 +8522,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AC50" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AD50" s="12" t="s">
         <x:v>50</x:v>
@@ -8531,7 +8534,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AG50" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AH50" s="12" t="s">
         <x:v>50</x:v>
@@ -8543,7 +8546,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK50" s="12" t="s">
-        <x:v>149</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AL50" s="12" t="s">
         <x:v>50</x:v>
@@ -8552,13 +8555,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AN50" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO50" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AP50" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ50" s="12">
         <x:v>38</x:v>
@@ -8567,7 +8570,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AS50" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT50" s="12" t="s">
         <x:v>53</x:v>
@@ -8579,7 +8582,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AW50" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AX50" s="12" t="s">
         <x:v>50</x:v>
@@ -8591,7 +8594,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="BA50" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BB50" s="12" t="s">
         <x:v>50</x:v>
@@ -8609,13 +8612,13 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG50" s="12">
-        <x:v>115</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="BH50" s="12" t="s">
         <x:v>150</x:v>
       </x:c>
       <x:c r="BI50" s="12">
-        <x:v>182</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="BJ50" s="12" t="s">
         <x:v>151</x:v>
@@ -8632,7 +8635,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E51" s="12" t="s">
         <x:v>53</x:v>
@@ -8644,7 +8647,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="H51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I51" s="12" t="s">
         <x:v>53</x:v>
@@ -8662,7 +8665,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="N51" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O51" s="12">
         <x:v>39</x:v>
@@ -8695,7 +8698,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="Y51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Z51" s="12" t="s">
         <x:v>50</x:v>
@@ -8731,7 +8734,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AK51" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AL51" s="12" t="s">
         <x:v>50</x:v>
@@ -8740,13 +8743,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AN51" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO51" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP51" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ51" s="12">
         <x:v>39</x:v>
@@ -8797,16 +8800,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG51" s="12">
-        <x:v>69</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="BH51" s="12" t="s">
-        <x:v>130</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BI51" s="12">
-        <x:v>126</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="BJ51" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:62">
@@ -8820,7 +8823,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E52" s="12" t="s">
         <x:v>50</x:v>
@@ -8832,7 +8835,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="I52" s="12" t="s">
         <x:v>50</x:v>
@@ -8844,7 +8847,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="L52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="M52" s="12" t="s">
         <x:v>50</x:v>
@@ -8856,7 +8859,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="P52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Q52" s="12" t="s">
         <x:v>50</x:v>
@@ -8868,7 +8871,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="T52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="U52" s="12" t="s">
         <x:v>50</x:v>
@@ -8880,7 +8883,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="X52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Y52" s="12" t="s">
         <x:v>50</x:v>
@@ -8892,7 +8895,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AB52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AC52" s="12" t="s">
         <x:v>50</x:v>
@@ -8904,7 +8907,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AF52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AG52" s="12" t="s">
         <x:v>50</x:v>
@@ -8916,7 +8919,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AJ52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AK52" s="12" t="s">
         <x:v>50</x:v>
@@ -8928,19 +8931,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AN52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AO52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="AR52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AS52" s="12" t="s">
         <x:v>50</x:v>
@@ -8952,7 +8955,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AV52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AW52" s="12" t="s">
         <x:v>50</x:v>
@@ -8964,7 +8967,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AZ52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BA52" s="12" t="s">
         <x:v>50</x:v>
@@ -8976,25 +8979,25 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="BD52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BE52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BF52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BG52" s="12">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BH52" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="BI52" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="BJ52" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:62">
@@ -9008,7 +9011,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E53" s="12" t="s">
         <x:v>50</x:v>
@@ -9020,7 +9023,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="I53" s="12" t="s">
         <x:v>50</x:v>
@@ -9032,7 +9035,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="L53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="M53" s="12" t="s">
         <x:v>50</x:v>
@@ -9044,7 +9047,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="P53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Q53" s="12" t="s">
         <x:v>50</x:v>
@@ -9056,7 +9059,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="T53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="U53" s="12" t="s">
         <x:v>50</x:v>
@@ -9068,7 +9071,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="X53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Y53" s="12" t="s">
         <x:v>50</x:v>
@@ -9080,7 +9083,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AB53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AC53" s="12" t="s">
         <x:v>50</x:v>
@@ -9092,7 +9095,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AF53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AG53" s="12" t="s">
         <x:v>50</x:v>
@@ -9104,7 +9107,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AJ53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AK53" s="12" t="s">
         <x:v>50</x:v>
@@ -9116,19 +9119,19 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AN53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AO53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ53" s="12">
         <x:v>41</x:v>
       </x:c>
       <x:c r="AR53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AS53" s="12" t="s">
         <x:v>50</x:v>
@@ -9140,7 +9143,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AV53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AW53" s="12" t="s">
         <x:v>50</x:v>
@@ -9152,7 +9155,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AZ53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BA53" s="12" t="s">
         <x:v>50</x:v>
@@ -9164,25 +9167,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="BD53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BE53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BF53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BG53" s="12">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BH53" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="BI53" s="12">
         <x:v>108</x:v>
       </x:c>
       <x:c r="BJ53" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:62">
@@ -9196,7 +9199,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="D54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E54" s="12" t="s">
         <x:v>50</x:v>
@@ -9208,7 +9211,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="I54" s="12" t="s">
         <x:v>50</x:v>
@@ -9220,7 +9223,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="M54" s="12" t="s">
         <x:v>50</x:v>
@@ -9232,7 +9235,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="P54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Q54" s="12" t="s">
         <x:v>50</x:v>
@@ -9244,7 +9247,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="T54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="U54" s="12" t="s">
         <x:v>50</x:v>
@@ -9256,7 +9259,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="X54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Y54" s="12" t="s">
         <x:v>50</x:v>
@@ -9268,7 +9271,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AB54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AC54" s="12" t="s">
         <x:v>50</x:v>
@@ -9280,7 +9283,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AF54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AG54" s="12" t="s">
         <x:v>50</x:v>
@@ -9292,7 +9295,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AJ54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AK54" s="12" t="s">
         <x:v>50</x:v>
@@ -9304,19 +9307,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AN54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AO54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="AR54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AS54" s="12" t="s">
         <x:v>50</x:v>
@@ -9328,7 +9331,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AV54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AW54" s="12" t="s">
         <x:v>50</x:v>
@@ -9340,7 +9343,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AZ54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BA54" s="12" t="s">
         <x:v>50</x:v>
@@ -9352,25 +9355,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="BD54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BE54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BF54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BG54" s="12">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BH54" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="BI54" s="12">
         <x:v>109</x:v>
       </x:c>
       <x:c r="BJ54" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:62">
@@ -9408,10 +9411,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="N55" s="12" t="s">
         <x:v>50</x:v>
@@ -9447,7 +9450,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Y55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Z55" s="12" t="s">
         <x:v>50</x:v>
@@ -9483,7 +9486,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK55" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AL55" s="12" t="s">
         <x:v>50</x:v>
@@ -9492,13 +9495,13 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AN55" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO55" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AP55" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ55" s="12">
         <x:v>43</x:v>
@@ -9507,7 +9510,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AS55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT55" s="12" t="s">
         <x:v>50</x:v>
@@ -9528,10 +9531,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AZ55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB55" s="12" t="s">
         <x:v>50</x:v>
@@ -9543,22 +9546,22 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="BE55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BF55" s="12" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG55" s="12">
-        <x:v>74</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="BH55" s="12" t="s">
         <x:v>157</x:v>
       </x:c>
       <x:c r="BI55" s="12">
-        <x:v>135</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="BJ55" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:62">
@@ -9572,7 +9575,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="D56" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E56" s="12" t="s">
         <x:v>49</x:v>
@@ -9596,7 +9599,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="L56" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M56" s="12" t="s">
         <x:v>50</x:v>
@@ -9608,7 +9611,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="P56" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q56" s="12" t="s">
         <x:v>50</x:v>
@@ -9644,7 +9647,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AB56" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AC56" s="12" t="s">
         <x:v>52</x:v>
@@ -9656,7 +9659,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AF56" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AG56" s="12" t="s">
         <x:v>50</x:v>
@@ -9680,13 +9683,13 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AN56" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO56" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP56" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ56" s="12">
         <x:v>44</x:v>
@@ -9728,7 +9731,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="BD56" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BE56" s="12" t="s">
         <x:v>49</x:v>
@@ -9737,16 +9740,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG56" s="12">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="BH56" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BI56" s="12">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="BJ56" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:62">
@@ -9760,7 +9763,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="D57" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E57" s="12" t="s">
         <x:v>52</x:v>
@@ -9820,7 +9823,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="X57" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Y57" s="12" t="s">
         <x:v>53</x:v>
@@ -9859,7 +9862,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AK57" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AL57" s="12" t="s">
         <x:v>50</x:v>
@@ -9868,13 +9871,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AN57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AP57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ57" s="12">
         <x:v>45</x:v>
@@ -9925,21 +9928,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG57" s="12">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BH57" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="BI57" s="12">
-        <x:v>50</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BJ57" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:62">
       <x:c r="A58" s="11" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B58" s="12" t="s">
         <x:v>47</x:v>
@@ -9948,7 +9951,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="D58" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E58" s="12" t="s">
         <x:v>52</x:v>
@@ -9960,10 +9963,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J58" s="12" t="s">
         <x:v>50</x:v>
@@ -9984,7 +9987,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="P58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q58" s="12" t="s">
         <x:v>49</x:v>
@@ -9996,7 +9999,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="T58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="U58" s="12" t="s">
         <x:v>52</x:v>
@@ -10008,7 +10011,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="X58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y58" s="12" t="s">
         <x:v>51</x:v>
@@ -10056,13 +10059,13 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AN58" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO58" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="AP58" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ58" s="12">
         <x:v>46</x:v>
@@ -10080,7 +10083,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AV58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AW58" s="12" t="s">
         <x:v>52</x:v>
@@ -10092,7 +10095,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AZ58" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BA58" s="12" t="s">
         <x:v>53</x:v>
@@ -10104,7 +10107,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="BD58" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE58" s="12" t="s">
         <x:v>53</x:v>
@@ -10113,21 +10116,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG58" s="12">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="BH58" s="12" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="BI58" s="12">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="BJ58" s="12" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="BH58" s="12" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="BI58" s="12">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="BJ58" s="12" t="s">
-        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:62">
       <x:c r="A59" s="11" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B59" s="12" t="s">
         <x:v>47</x:v>
@@ -10139,7 +10142,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="E59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F59" s="12" t="s">
         <x:v>50</x:v>
@@ -10160,10 +10163,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="L59" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M59" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="N59" s="12" t="s">
         <x:v>50</x:v>
@@ -10199,7 +10202,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="Y59" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z59" s="12" t="s">
         <x:v>50</x:v>
@@ -10211,7 +10214,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AC59" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AD59" s="12" t="s">
         <x:v>50</x:v>
@@ -10223,7 +10226,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AG59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH59" s="12" t="s">
         <x:v>50</x:v>
@@ -10244,13 +10247,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AN59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ59" s="12">
         <x:v>47</x:v>
@@ -10259,7 +10262,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AS59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT59" s="12" t="s">
         <x:v>50</x:v>
@@ -10271,7 +10274,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AW59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AX59" s="12" t="s">
         <x:v>50</x:v>
@@ -10283,7 +10286,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="BA59" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="BB59" s="12" t="s">
         <x:v>50</x:v>
@@ -10301,21 +10304,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG59" s="12">
-        <x:v>101</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="BH59" s="12" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="BI59" s="12">
-        <x:v>101</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="BJ59" s="12" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:62">
       <x:c r="A60" s="11" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
         <x:v>47</x:v>
@@ -10384,10 +10387,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="X60" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y60" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Z60" s="12" t="s">
         <x:v>50</x:v>
@@ -10399,7 +10402,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AC60" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AD60" s="12" t="s">
         <x:v>50</x:v>
@@ -10423,7 +10426,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK60" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL60" s="12" t="s">
         <x:v>50</x:v>
@@ -10432,13 +10435,13 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AN60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AP60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ60" s="12">
         <x:v>48</x:v>
@@ -10447,7 +10450,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AS60" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT60" s="12" t="s">
         <x:v>50</x:v>
@@ -10489,21 +10492,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG60" s="12">
-        <x:v>72</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="BH60" s="12" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BI60" s="12">
-        <x:v>72</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="BJ60" s="12" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:62">
       <x:c r="A61" s="11" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B61" s="12" t="s">
         <x:v>47</x:v>
@@ -10539,7 +10542,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M61" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="N61" s="12" t="s">
         <x:v>50</x:v>
@@ -10572,10 +10575,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="X61" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y61" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Z61" s="12" t="s">
         <x:v>50</x:v>
@@ -10587,7 +10590,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AC61" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AD61" s="12" t="s">
         <x:v>50</x:v>
@@ -10596,7 +10599,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AF61" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AG61" s="12" t="s">
         <x:v>50</x:v>
@@ -10620,13 +10623,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AN61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ61" s="12">
         <x:v>49</x:v>
@@ -10677,21 +10680,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG61" s="12">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="BH61" s="12" t="s">
-        <x:v>125</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BI61" s="12">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="BJ61" s="12" t="s">
-        <x:v>125</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:62">
       <x:c r="A62" s="11" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B62" s="12" t="s">
         <x:v>47</x:v>
@@ -10808,13 +10811,13 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AN62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ62" s="12">
         <x:v>50</x:v>
@@ -10865,16 +10868,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG62" s="12">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="BH62" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="BI62" s="12">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="BJ62" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:62">
@@ -10984,7 +10987,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AJ63" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AK63" s="12" t="s">
         <x:v>55</x:v>
@@ -10996,19 +10999,19 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AN63" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="AO63" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AP63" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AQ63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AR63" s="12" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="AO63" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="AP63" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="AQ63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="AR63" s="12" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="AS63" s="12" t="s">
         <x:v>50</x:v>
@@ -11053,105 +11056,105 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BG63" s="12">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="BH63" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="BI63" s="12">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="BJ63" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:62">
       <x:c r="A64" s="13" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B64" s="13" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C64" s="7" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="D64" s="7"/>
       <x:c r="E64" s="7"/>
       <x:c r="F64" s="7"/>
       <x:c r="G64" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H64" s="7"/>
       <x:c r="I64" s="7"/>
       <x:c r="J64" s="7"/>
       <x:c r="K64" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="L64" s="7"/>
       <x:c r="M64" s="7"/>
       <x:c r="N64" s="7"/>
       <x:c r="O64" s="7" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="P64" s="7"/>
       <x:c r="Q64" s="7"/>
       <x:c r="R64" s="7"/>
       <x:c r="S64" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="T64" s="7"/>
       <x:c r="U64" s="7"/>
       <x:c r="V64" s="7"/>
       <x:c r="W64" s="7" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="X64" s="7"/>
       <x:c r="Y64" s="7"/>
       <x:c r="Z64" s="7"/>
       <x:c r="AA64" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="AB64" s="7"/>
       <x:c r="AC64" s="7"/>
       <x:c r="AD64" s="7"/>
       <x:c r="AE64" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="AF64" s="7"/>
       <x:c r="AG64" s="7"/>
       <x:c r="AH64" s="7"/>
       <x:c r="AI64" s="7" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="AJ64" s="7"/>
       <x:c r="AK64" s="7"/>
       <x:c r="AL64" s="7"/>
       <x:c r="AM64" s="7" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="AN64" s="7"/>
       <x:c r="AO64" s="7"/>
       <x:c r="AP64" s="7"/>
       <x:c r="AQ64" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="AR64" s="7"/>
       <x:c r="AS64" s="7"/>
       <x:c r="AT64" s="7"/>
       <x:c r="AU64" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="AV64" s="7"/>
       <x:c r="AW64" s="7"/>
       <x:c r="AX64" s="7"/>
       <x:c r="AY64" s="7" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="AZ64" s="7"/>
       <x:c r="BA64" s="7"/>
       <x:c r="BB64" s="7"/>
       <x:c r="BC64" s="7" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="BD64" s="7"/>
       <x:c r="BE64" s="7"/>
@@ -11163,37 +11166,37 @@
     </x:row>
     <x:row r="66" spans="1:62">
       <x:c r="A66" s="14" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:62">
       <x:c r="A67" s="13" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:62">
       <x:c r="A68" s="13" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:62">
       <x:c r="A69" s="13" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:62">
       <x:c r="A70" s="13" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:62">
       <x:c r="A71" s="13" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:62">
       <x:c r="A72" s="13" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
